--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -642,7 +642,7 @@
         <v>0.4885960000000001</v>
       </c>
       <c r="G5">
-        <v>0.03440399999999988</v>
+        <v>0.03440399999999993</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -665,7 +665,7 @@
         <v>0.4995673824154764</v>
       </c>
       <c r="G6">
-        <v>0.02343261758452364</v>
+        <v>0.02343261758452359</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -846,10 +846,10 @@
         <v>0.443</v>
       </c>
       <c r="F14">
-        <v>0.47619831814436</v>
+        <v>0.4761983181443601</v>
       </c>
       <c r="G14">
-        <v>0.03319831814436003</v>
+        <v>0.03319831814436008</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5400,10 +5400,10 @@
         <v>0.449</v>
       </c>
       <c r="F212">
-        <v>0.4773119999999993</v>
+        <v>0.4773119999999992</v>
       </c>
       <c r="G212">
-        <v>0.02831199999999928</v>
+        <v>0.02831199999999923</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -5633,7 +5633,7 @@
         <v>0.4917381479293702</v>
       </c>
       <c r="G222">
-        <v>0.02526185207062981</v>
+        <v>0.02526185207062986</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -10207,10 +10207,10 @@
         <v>0.455</v>
       </c>
       <c r="F421">
-        <v>0.4830239999999993</v>
+        <v>0.4830239999999994</v>
       </c>
       <c r="G421">
-        <v>0.02802399999999933</v>
+        <v>0.02802399999999938</v>
       </c>
     </row>
     <row r="422" spans="1:7">
@@ -10230,10 +10230,10 @@
         <v>0.455</v>
       </c>
       <c r="F422">
-        <v>0.481056714755704</v>
+        <v>0.4810567147557039</v>
       </c>
       <c r="G422">
-        <v>0.02605671475570398</v>
+        <v>0.02605671475570387</v>
       </c>
     </row>
     <row r="423" spans="1:7">
@@ -10414,10 +10414,10 @@
         <v>0.512</v>
       </c>
       <c r="F430">
-        <v>0.4895113339758257</v>
+        <v>0.4895113339758256</v>
       </c>
       <c r="G430">
-        <v>0.02248866602417432</v>
+        <v>0.02248866602417443</v>
       </c>
     </row>
     <row r="431" spans="1:7">
@@ -15014,10 +15014,10 @@
         <v>0.534</v>
       </c>
       <c r="F630">
-        <v>0.4837637674792231</v>
+        <v>0.483763767479223</v>
       </c>
       <c r="G630">
-        <v>0.05023623252077697</v>
+        <v>0.05023623252077702</v>
       </c>
     </row>
     <row r="631" spans="1:7">
@@ -15175,10 +15175,10 @@
         <v>0.448</v>
       </c>
       <c r="F637">
-        <v>0.4865799999999995</v>
+        <v>0.4865799999999994</v>
       </c>
       <c r="G637">
-        <v>0.03857999999999945</v>
+        <v>0.03857999999999939</v>
       </c>
     </row>
     <row r="638" spans="1:7">
@@ -15198,10 +15198,10 @@
         <v>0.448</v>
       </c>
       <c r="F638">
-        <v>0.4843105651824637</v>
+        <v>0.4843105651824636</v>
       </c>
       <c r="G638">
-        <v>0.03631056518246373</v>
+        <v>0.03631056518246362</v>
       </c>
     </row>
     <row r="639" spans="1:7">
@@ -19798,10 +19798,10 @@
         <v>0.473</v>
       </c>
       <c r="F838">
-        <v>0.4794602172888913</v>
+        <v>0.4794602172888914</v>
       </c>
       <c r="G838">
-        <v>0.006460217288891346</v>
+        <v>0.006460217288891401</v>
       </c>
     </row>
     <row r="839" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -5426,7 +5426,7 @@
         <v>0.4815039999999993</v>
       </c>
       <c r="G213">
-        <v>0.03250399999999926</v>
+        <v>0.03250399999999931</v>
       </c>
     </row>
     <row r="214" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -1664,10 +1664,10 @@
         <v>0.534</v>
       </c>
       <c r="F54">
-        <v>0.4861041134543477</v>
+        <v>0.4861041134543476</v>
       </c>
       <c r="G54">
-        <v>0.04789588654565236</v>
+        <v>0.04789588654565247</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1848,10 +1848,10 @@
         <v>0.448</v>
       </c>
       <c r="F62">
-        <v>0.48175965890575</v>
+        <v>0.4817596589057499</v>
       </c>
       <c r="G62">
-        <v>0.03375965890575</v>
+        <v>0.03375965890574989</v>
       </c>
     </row>
     <row r="63" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -1664,10 +1664,10 @@
         <v>0.534</v>
       </c>
       <c r="F54">
-        <v>0.4861041134543476</v>
+        <v>0.4861041134543477</v>
       </c>
       <c r="G54">
-        <v>0.04789588654565247</v>
+        <v>0.04789588654565236</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1848,10 +1848,10 @@
         <v>0.448</v>
       </c>
       <c r="F62">
-        <v>0.4817596589057499</v>
+        <v>0.48175965890575</v>
       </c>
       <c r="G62">
-        <v>0.03375965890574989</v>
+        <v>0.03375965890575</v>
       </c>
     </row>
     <row r="63" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -560,10 +560,10 @@
         <v>0.523</v>
       </c>
       <c r="F6">
-        <v>0.5007342175162359</v>
+        <v>0.500734217516236</v>
       </c>
       <c r="G6">
-        <v>0.0222657824837641</v>
+        <v>0.02226578248376399</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -928,10 +928,10 @@
         <v>0.449</v>
       </c>
       <c r="F22">
-        <v>0.4760588018293675</v>
+        <v>0.4760588018293674</v>
       </c>
       <c r="G22">
-        <v>0.02705880182936748</v>
+        <v>0.02705880182936743</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1112,10 +1112,10 @@
         <v>0.517</v>
       </c>
       <c r="F30">
-        <v>0.4950339368661047</v>
+        <v>0.4950339368661046</v>
       </c>
       <c r="G30">
-        <v>0.02196606313389532</v>
+        <v>0.02196606313389537</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1664,10 +1664,10 @@
         <v>0.534</v>
       </c>
       <c r="F54">
-        <v>0.4861041134543477</v>
+        <v>0.4861041134543476</v>
       </c>
       <c r="G54">
-        <v>0.04789588654565236</v>
+        <v>0.04789588654565247</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1848,10 +1848,10 @@
         <v>0.448</v>
       </c>
       <c r="F62">
-        <v>0.48175965890575</v>
+        <v>0.4817596589057499</v>
       </c>
       <c r="G62">
-        <v>0.03375965890575</v>
+        <v>0.03375965890574989</v>
       </c>
     </row>
     <row r="63" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -560,10 +560,10 @@
         <v>0.523</v>
       </c>
       <c r="F6">
-        <v>0.500734217516236</v>
+        <v>0.5007342175162359</v>
       </c>
       <c r="G6">
-        <v>0.02226578248376399</v>
+        <v>0.0222657824837641</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -928,10 +928,10 @@
         <v>0.449</v>
       </c>
       <c r="F22">
-        <v>0.4760588018293674</v>
+        <v>0.4760588018293675</v>
       </c>
       <c r="G22">
-        <v>0.02705880182936743</v>
+        <v>0.02705880182936748</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1112,10 +1112,10 @@
         <v>0.517</v>
       </c>
       <c r="F30">
-        <v>0.4950339368661046</v>
+        <v>0.4950339368661047</v>
       </c>
       <c r="G30">
-        <v>0.02196606313389537</v>
+        <v>0.02196606313389532</v>
       </c>
     </row>
     <row r="31" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -928,10 +928,10 @@
         <v>0.449</v>
       </c>
       <c r="F22">
-        <v>0.4760588018293675</v>
+        <v>0.4760588018293676</v>
       </c>
       <c r="G22">
-        <v>0.02705880182936748</v>
+        <v>0.02705880182936754</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1112,10 +1112,10 @@
         <v>0.517</v>
       </c>
       <c r="F30">
-        <v>0.4950339368661047</v>
+        <v>0.4950339368661048</v>
       </c>
       <c r="G30">
-        <v>0.02196606313389532</v>
+        <v>0.02196606313389526</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1276,7 +1276,7 @@
         <v>0.4846759999999996</v>
       </c>
       <c r="G37">
-        <v>0.02967599999999959</v>
+        <v>0.02967599999999954</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1299,7 +1299,7 @@
         <v>0.4859622591660155</v>
       </c>
       <c r="G38">
-        <v>0.03096225916601553</v>
+        <v>0.03096225916601547</v>
       </c>
     </row>
     <row r="39" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -928,10 +928,10 @@
         <v>0.449</v>
       </c>
       <c r="F22">
-        <v>0.4760588018293676</v>
+        <v>0.4760588018293675</v>
       </c>
       <c r="G22">
-        <v>0.02705880182936754</v>
+        <v>0.02705880182936748</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1112,10 +1112,10 @@
         <v>0.517</v>
       </c>
       <c r="F30">
-        <v>0.4950339368661048</v>
+        <v>0.4950339368661047</v>
       </c>
       <c r="G30">
-        <v>0.02196606313389526</v>
+        <v>0.02196606313389532</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1276,7 +1276,7 @@
         <v>0.4846759999999996</v>
       </c>
       <c r="G37">
-        <v>0.02967599999999954</v>
+        <v>0.02967599999999959</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1299,7 +1299,7 @@
         <v>0.4859622591660155</v>
       </c>
       <c r="G38">
-        <v>0.03096225916601547</v>
+        <v>0.03096225916601553</v>
       </c>
     </row>
     <row r="39" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -1276,7 +1276,7 @@
         <v>0.4846759999999996</v>
       </c>
       <c r="G37">
-        <v>0.02967599999999959</v>
+        <v>0.02967599999999954</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1299,7 +1299,7 @@
         <v>0.4859622591660155</v>
       </c>
       <c r="G38">
-        <v>0.03096225916601553</v>
+        <v>0.03096225916601547</v>
       </c>
     </row>
     <row r="39" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -560,10 +560,10 @@
         <v>0.523</v>
       </c>
       <c r="F6">
-        <v>0.5007342175162359</v>
+        <v>0.500734217516236</v>
       </c>
       <c r="G6">
-        <v>0.0222657824837641</v>
+        <v>0.02226578248376399</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1641,10 +1641,10 @@
         <v>0.534</v>
       </c>
       <c r="F53">
-        <v>0.4821359999999988</v>
+        <v>0.4821359999999989</v>
       </c>
       <c r="G53">
-        <v>0.05186400000000119</v>
+        <v>0.05186400000000113</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1664,10 +1664,10 @@
         <v>0.534</v>
       </c>
       <c r="F54">
-        <v>0.4861041134543476</v>
+        <v>0.4861041134543477</v>
       </c>
       <c r="G54">
-        <v>0.04789588654565247</v>
+        <v>0.04789588654565236</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1848,10 +1848,10 @@
         <v>0.448</v>
       </c>
       <c r="F62">
-        <v>0.4817596589057499</v>
+        <v>0.48175965890575</v>
       </c>
       <c r="G62">
-        <v>0.03375965890574989</v>
+        <v>0.03375965890575</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1986,10 +1986,10 @@
         <v>0.473</v>
       </c>
       <c r="F68">
-        <v>0.464931999999999</v>
+        <v>0.4649319999999991</v>
       </c>
       <c r="G68">
-        <v>0.008068000000000963</v>
+        <v>0.008068000000000908</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2219,7 +2219,7 @@
         <v>0.4996373659320615</v>
       </c>
       <c r="G78">
-        <v>0.000362634067938461</v>
+        <v>0.0003626340679385165</v>
       </c>
     </row>
     <row r="79" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -724,7 +724,7 @@
         <v>0.4837719999999988</v>
       </c>
       <c r="G13">
-        <v>0.04077199999999875</v>
+        <v>0.04077199999999881</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -928,10 +928,10 @@
         <v>0.449</v>
       </c>
       <c r="F22">
-        <v>0.4760588018293675</v>
+        <v>0.4760588018293676</v>
       </c>
       <c r="G22">
-        <v>0.02705880182936748</v>
+        <v>0.02705880182936754</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1112,10 +1112,10 @@
         <v>0.517</v>
       </c>
       <c r="F30">
-        <v>0.4950339368661047</v>
+        <v>0.4950339368661048</v>
       </c>
       <c r="G30">
-        <v>0.02196606313389532</v>
+        <v>0.02196606313389526</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1273,10 +1273,10 @@
         <v>0.455</v>
       </c>
       <c r="F37">
-        <v>0.4846759999999996</v>
+        <v>0.4846759999999995</v>
       </c>
       <c r="G37">
-        <v>0.02967599999999954</v>
+        <v>0.02967599999999948</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1296,10 +1296,10 @@
         <v>0.455</v>
       </c>
       <c r="F38">
-        <v>0.4859622591660155</v>
+        <v>0.4859622591660154</v>
       </c>
       <c r="G38">
-        <v>0.03096225916601547</v>
+        <v>0.03096225916601542</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1483,7 +1483,7 @@
         <v>0.485489875827558</v>
       </c>
       <c r="G46">
-        <v>0.02651012417244197</v>
+        <v>0.02651012417244203</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1641,10 +1641,10 @@
         <v>0.534</v>
       </c>
       <c r="F53">
-        <v>0.4821359999999989</v>
+        <v>0.4821359999999988</v>
       </c>
       <c r="G53">
-        <v>0.05186400000000113</v>
+        <v>0.05186400000000119</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2219,7 +2219,7 @@
         <v>0.4996373659320615</v>
       </c>
       <c r="G78">
-        <v>0.0003626340679385165</v>
+        <v>0.000362634067938461</v>
       </c>
     </row>
     <row r="79" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -560,10 +560,10 @@
         <v>0.523</v>
       </c>
       <c r="F6">
-        <v>0.500734217516236</v>
+        <v>0.5007342175162359</v>
       </c>
       <c r="G6">
-        <v>0.02226578248376399</v>
+        <v>0.0222657824837641</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -724,7 +724,7 @@
         <v>0.4837719999999988</v>
       </c>
       <c r="G13">
-        <v>0.04077199999999881</v>
+        <v>0.04077199999999875</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -928,10 +928,10 @@
         <v>0.449</v>
       </c>
       <c r="F22">
-        <v>0.4760588018293676</v>
+        <v>0.4760588018293675</v>
       </c>
       <c r="G22">
-        <v>0.02705880182936754</v>
+        <v>0.02705880182936748</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1112,10 +1112,10 @@
         <v>0.517</v>
       </c>
       <c r="F30">
-        <v>0.4950339368661048</v>
+        <v>0.4950339368661047</v>
       </c>
       <c r="G30">
-        <v>0.02196606313389526</v>
+        <v>0.02196606313389532</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1273,10 +1273,10 @@
         <v>0.455</v>
       </c>
       <c r="F37">
-        <v>0.4846759999999995</v>
+        <v>0.4846759999999996</v>
       </c>
       <c r="G37">
-        <v>0.02967599999999948</v>
+        <v>0.02967599999999959</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1296,10 +1296,10 @@
         <v>0.455</v>
       </c>
       <c r="F38">
-        <v>0.4859622591660154</v>
+        <v>0.4859622591660155</v>
       </c>
       <c r="G38">
-        <v>0.03096225916601542</v>
+        <v>0.03096225916601553</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1483,7 +1483,7 @@
         <v>0.485489875827558</v>
       </c>
       <c r="G46">
-        <v>0.02651012417244203</v>
+        <v>0.02651012417244197</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1986,10 +1986,10 @@
         <v>0.473</v>
       </c>
       <c r="F68">
-        <v>0.4649319999999991</v>
+        <v>0.464931999999999</v>
       </c>
       <c r="G68">
-        <v>0.008068000000000908</v>
+        <v>0.008068000000000963</v>
       </c>
     </row>
     <row r="69" spans="1:7">

--- a/outputs/Block2_Nested_LOEO_Details_v12.xlsx
+++ b/outputs/Block2_Nested_LOEO_Details_v12.xlsx
@@ -2216,10 +2216,10 @@
         <v>0.5</v>
       </c>
       <c r="F78">
-        <v>0.4996373659320615</v>
+        <v>0.4996373659320614</v>
       </c>
       <c r="G78">
-        <v>0.000362634067938461</v>
+        <v>0.000362634067938572</v>
       </c>
     </row>
     <row r="79" spans="1:7">
